--- a/Demo-Data/Live-Demo-2-Results.xlsx
+++ b/Demo-Data/Live-Demo-2-Results.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{3519167B-3895-49EC-B743-B92267A3CF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECB0D602-8979-4340-B833-173084747AA2}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{3519167B-3895-49EC-B743-B92267A3CF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66F7C608-3FAC-4A83-B85E-86E18648F77C}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" tabRatio="733" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="733" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Results" sheetId="7" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId7"/>
+    <pivotCache cacheId="7" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -335,7 +335,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -518,17 +518,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
@@ -550,7 +541,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -560,10 +551,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -593,7 +580,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,10 +615,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1314,7 +1305,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E13711-E10D-456F-9762-18B8A49207DB}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E13711-E10D-456F-9762-18B8A49207DB}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -1712,1186 +1703,1185 @@
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="14" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="17" t="s">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2">
         <v>45</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="17" t="s">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="C3" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3">
         <v>24</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="17" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4">
         <v>615</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="17" t="s">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="C5" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5">
         <v>253</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="17" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="C6" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6">
         <v>1800</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D7" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7">
         <v>0.1</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="17" t="s">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D8" s="17" t="s">
+      <c r="C8" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D8" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8">
         <v>694</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="17" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9">
         <v>2340</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="17" t="s">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="C10" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D10" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10">
         <v>26</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="17" t="s">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D11" s="17" t="s">
+      <c r="C11" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D11" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="17" t="s">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D12" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12">
         <v>50</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="17" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="C13" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D13" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13">
         <v>2150</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="17" t="s">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D14" s="17" t="s">
+      <c r="C14" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D14" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14">
         <v>837</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="17" t="s">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D15" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15">
         <v>0.2</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="17" t="s">
+      <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D16" s="17" t="s">
+      <c r="C16" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D16" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16">
         <v>88</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="17" t="s">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D17" s="17" t="s">
+      <c r="C17" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D17" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17">
         <v>5310</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="17" t="s">
+      <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D18" s="17" t="s">
+      <c r="C18" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D18" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18">
         <v>11</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="17" t="s">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D19" s="17" t="s">
+      <c r="C19" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D19" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="17" t="s">
+      <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D20" s="17" t="s">
+      <c r="C20" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D20" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20">
         <v>42</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="17" t="s">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="C21" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D21" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21">
         <v>23</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="17" t="s">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D22" s="17" t="s">
+      <c r="C22" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D22" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22">
         <v>22</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="17" t="s">
+      <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D23" s="17" t="s">
+      <c r="C23" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D23" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23">
         <v>0.1</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="17" t="s">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D24" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24">
         <v>37</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="17" t="s">
+      <c r="A25" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D25" s="17" t="s">
+      <c r="C25" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D25" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25">
         <v>72</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="17" t="s">
+      <c r="A26" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D26" s="17" t="s">
+      <c r="C26" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="17" t="s">
+      <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D27" s="17" t="s">
+      <c r="C27" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D27" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="17" t="s">
+      <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D28" s="17" t="s">
+      <c r="C28" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D28" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28">
         <v>28</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="17" t="s">
+      <c r="A29" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D29" s="17" t="s">
+      <c r="C29" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D29" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29">
         <v>49</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="17" t="s">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D30" s="17" t="s">
+      <c r="C30" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D30" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30">
         <v>184</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="17" t="s">
+      <c r="A31" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D31" s="17" t="s">
+      <c r="C31" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D31" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31">
         <v>0.1</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="17" t="s">
+      <c r="A32" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D32" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32">
         <v>26</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="17" t="s">
+      <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D33" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33">
         <v>225</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="17" t="s">
+      <c r="A34" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D34" s="17" t="s">
+      <c r="C34" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D34" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34">
         <v>5</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="17" t="s">
+      <c r="A35" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D35" s="17" t="s">
+      <c r="C35" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D35" t="s">
         <v>2</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" t="s">
         <v>80</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="17" t="s">
+      <c r="A36" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D36" s="17" t="s">
+      <c r="C36" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D36" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36">
         <v>56</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="17" t="s">
+      <c r="A37" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D37" s="17" t="s">
+      <c r="C37" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D37" t="s">
         <v>4</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37">
         <v>22</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="17" t="s">
+      <c r="A38" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D38" s="17" t="s">
+      <c r="C38" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D38" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38">
         <v>26</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G38" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="17" t="s">
+      <c r="A39" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D39" s="17" t="s">
+      <c r="C39" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D39" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39">
         <v>0.1</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="17" t="s">
+      <c r="A40" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D40" s="17" t="s">
+      <c r="C40" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D40" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F40">
         <v>55</v>
       </c>
-      <c r="G40" s="17" t="s">
+      <c r="G40" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="17" t="s">
+      <c r="A41" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D41" s="17" t="s">
+      <c r="C41" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D41" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="17">
+      <c r="F41">
         <v>344</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="G41" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="17" t="s">
+      <c r="A42" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D42" s="17" t="s">
+      <c r="C42" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D42" t="s">
         <v>1</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42">
         <v>12</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="G42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="17" t="s">
+      <c r="A43" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D43" t="s">
         <v>2</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43">
         <v>2</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="17" t="s">
+      <c r="A44" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D44" s="17" t="s">
+      <c r="C44" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D44" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44">
         <v>34</v>
       </c>
-      <c r="G44" s="17" t="s">
+      <c r="G44" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="17" t="s">
+      <c r="A45" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D45" s="17" t="s">
+      <c r="C45" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D45" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45">
         <v>1460</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G45" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="17" t="s">
+      <c r="A46" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D46" s="17" t="s">
+      <c r="C46" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D46" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46">
         <v>557</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="G46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="17" t="s">
+      <c r="A47" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D47" s="17" t="s">
+      <c r="C47" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D47" t="s">
         <v>6</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" t="s">
         <v>80</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47">
         <v>0.1</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="G47" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="17" t="s">
+      <c r="A48" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D48" s="17" t="s">
+      <c r="C48" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D48" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48">
         <v>80</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G48" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="17" t="s">
+      <c r="A49" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D49" s="17" t="s">
+      <c r="C49" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D49" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49">
         <v>30000</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="G49" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="17" t="s">
+      <c r="A50" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" t="s">
         <v>63</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" t="s">
         <v>1</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" t="s">
         <v>80</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50">
         <v>5</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="17" t="s">
+      <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" t="s">
         <v>63</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" t="s">
         <v>2</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" t="s">
         <v>80</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="17" t="s">
+      <c r="A52" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52">
         <v>52</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="G52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="17" t="s">
+      <c r="A53" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" t="s">
         <v>4</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53">
         <v>43</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="17" t="s">
+      <c r="A54" t="s">
         <v>51</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54">
         <v>68</v>
       </c>
-      <c r="G54" s="17" t="s">
+      <c r="G54" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="17" t="s">
+      <c r="A55" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" t="s">
         <v>6</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55">
         <v>0.1</v>
       </c>
-      <c r="G55" s="17" t="s">
+      <c r="G55" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="17" t="s">
+      <c r="A56" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56">
         <v>79</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="G56" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="17" t="s">
+      <c r="A57" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" t="s">
         <v>63</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57">
         <v>1950</v>
       </c>
-      <c r="G57" s="17" t="s">
+      <c r="G57" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2995,68 +2985,66 @@
   <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="17"/>
-    <col min="11" max="12" width="10" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="17" t="s">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2">
         <v>45</v>
       </c>
-      <c r="G2" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="17" t="str">
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="str">
         <f>IF(
    IF(E2="&lt;",F2/2,F2) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D2,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D2,Criteria!A:A,Criteria!B:B))-1)),
@@ -3065,7 +3053,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I2" s="17" t="str">
+      <c r="I2" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D2,
@@ -3082,25 +3070,25 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="17" t="s">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="C3" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3">
         <v>24</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="17" t="str">
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="str">
         <f>IF(
    IF(E3="&lt;",F3/2,F3) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D3,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D3,Criteria!A:A,Criteria!B:B))-1)),
@@ -3109,7 +3097,7 @@
 )</f>
         <v>Exceeds</v>
       </c>
-      <c r="I3" s="17" t="str">
+      <c r="I3" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D3,
@@ -3126,25 +3114,25 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="17" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4">
         <v>615</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="17" t="e">
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="e">
         <f>IF(
    IF(E4="&lt;",F4/2,F4) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D4,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D4,Criteria!A:A,Criteria!B:B))-1)),
@@ -3153,7 +3141,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I4" s="17" t="str">
+      <c r="I4" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D4,
@@ -3170,25 +3158,25 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="17" t="s">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="C5" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5">
         <v>253</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="17" t="str">
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="str">
         <f>IF(
    IF(E5="&lt;",F5/2,F5) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D5,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D5,Criteria!A:A,Criteria!B:B))-1)),
@@ -3197,7 +3185,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I5" s="17" t="str">
+      <c r="I5" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D5,
@@ -3214,25 +3202,25 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="17" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="C6" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6">
         <v>1800</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="17" t="str">
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="str">
         <f>IF(
    IF(E6="&lt;",F6/2,F6) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D6,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D6,Criteria!A:A,Criteria!B:B))-1)),
@@ -3241,7 +3229,7 @@
 )</f>
         <v>Exceeds</v>
       </c>
-      <c r="I6" s="17" t="str">
+      <c r="I6" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D6,
@@ -3258,25 +3246,25 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="17" t="s">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D7" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7">
         <v>0.1</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="17" t="str">
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="str">
         <f>IF(
    IF(E7="&lt;",F7/2,F7) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D7,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D7,Criteria!A:A,Criteria!B:B))-1)),
@@ -3285,7 +3273,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I7" s="17" t="str">
+      <c r="I7" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D7,
@@ -3302,25 +3290,25 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="17" t="s">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D8" s="17" t="s">
+      <c r="C8" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D8" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8">
         <v>694</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="17" t="str">
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="str">
         <f>IF(
    IF(E8="&lt;",F8/2,F8) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D8,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D8,Criteria!A:A,Criteria!B:B))-1)),
@@ -3329,7 +3317,7 @@
 )</f>
         <v>Exceeds</v>
       </c>
-      <c r="I8" s="17" t="str">
+      <c r="I8" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D8,
@@ -3346,25 +3334,25 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9">
         <v>2340</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="17" t="str">
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="str">
         <f>IF(
    IF(E9="&lt;",F9/2,F9) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D9,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D9,Criteria!A:A,Criteria!B:B))-1)),
@@ -3373,7 +3361,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I9" s="17" t="str">
+      <c r="I9" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D9,
@@ -3390,25 +3378,25 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="17" t="s">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="C10" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D10" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10">
         <v>26</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="17" t="str">
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="str">
         <f>IF(
    IF(E10="&lt;",F10/2,F10) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D10,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D10,Criteria!A:A,Criteria!B:B))-1)),
@@ -3417,7 +3405,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I10" s="17" t="str">
+      <c r="I10" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D10,
@@ -3434,25 +3422,25 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="17" t="s">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D11" s="17" t="s">
+      <c r="C11" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D11" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="17" t="str">
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="str">
         <f>IF(
    IF(E11="&lt;",F11/2,F11) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D11,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D11,Criteria!A:A,Criteria!B:B))-1)),
@@ -3461,7 +3449,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I11" s="17" t="str">
+      <c r="I11" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D11,
@@ -3478,25 +3466,25 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="17" t="s">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D12" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12">
         <v>50</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="17" t="e">
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="e">
         <f>IF(
    IF(E12="&lt;",F12/2,F12) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D12,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D12,Criteria!A:A,Criteria!B:B))-1)),
@@ -3505,7 +3493,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I12" s="17" t="str">
+      <c r="I12" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D12,
@@ -3522,25 +3510,25 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="17" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="C13" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D13" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13">
         <v>2150</v>
       </c>
-      <c r="G13" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="17" t="str">
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" t="str">
         <f>IF(
    IF(E13="&lt;",F13/2,F13) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D13,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D13,Criteria!A:A,Criteria!B:B))-1)),
@@ -3549,7 +3537,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I13" s="17" t="str">
+      <c r="I13" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D13,
@@ -3566,25 +3554,25 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="17" t="s">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D14" s="17" t="s">
+      <c r="C14" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D14" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14">
         <v>837</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="17" t="str">
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" t="str">
         <f>IF(
    IF(E14="&lt;",F14/2,F14) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D14,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D14,Criteria!A:A,Criteria!B:B))-1)),
@@ -3593,7 +3581,7 @@
 )</f>
         <v>Exceeds</v>
       </c>
-      <c r="I14" s="17" t="str">
+      <c r="I14" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D14,
@@ -3610,25 +3598,25 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="17" t="s">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D15" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15">
         <v>0.2</v>
       </c>
-      <c r="G15" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="17" t="str">
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" t="str">
         <f>IF(
    IF(E15="&lt;",F15/2,F15) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D15,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D15,Criteria!A:A,Criteria!B:B))-1)),
@@ -3637,7 +3625,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I15" s="17" t="str">
+      <c r="I15" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D15,
@@ -3654,25 +3642,25 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="17" t="s">
+      <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D16" s="17" t="s">
+      <c r="C16" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D16" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16">
         <v>88</v>
       </c>
-      <c r="G16" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="17" t="str">
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" t="str">
         <f>IF(
    IF(E16="&lt;",F16/2,F16) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D16,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D16,Criteria!A:A,Criteria!B:B))-1)),
@@ -3681,7 +3669,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I16" s="17" t="str">
+      <c r="I16" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D16,
@@ -3698,25 +3686,25 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="17" t="s">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D17" s="17" t="s">
+      <c r="C17" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D17" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17">
         <v>5310</v>
       </c>
-      <c r="G17" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="17" t="str">
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="str">
         <f>IF(
    IF(E17="&lt;",F17/2,F17) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D17,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D17,Criteria!A:A,Criteria!B:B))-1)),
@@ -3725,7 +3713,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I17" s="17" t="str">
+      <c r="I17" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D17,
@@ -3742,25 +3730,25 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="17" t="s">
+      <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D18" s="17" t="s">
+      <c r="C18" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D18" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18">
         <v>11</v>
       </c>
-      <c r="G18" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="17" t="str">
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="str">
         <f>IF(
    IF(E18="&lt;",F18/2,F18) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D18,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D18,Criteria!A:A,Criteria!B:B))-1)),
@@ -3769,7 +3757,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I18" s="17" t="str">
+      <c r="I18" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D18,
@@ -3786,28 +3774,28 @@
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="17" t="s">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D19" s="17" t="s">
+      <c r="C19" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D19" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="17" t="str">
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" t="str">
         <f>IF(
    IF(E19="&lt;",F19/2,F19) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D19,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D19,Criteria!A:A,Criteria!B:B))-1)),
@@ -3816,7 +3804,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I19" s="17" t="str">
+      <c r="I19" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D19,
@@ -3833,25 +3821,25 @@
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="17" t="s">
+      <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D20" s="17" t="s">
+      <c r="C20" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D20" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20">
         <v>42</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="17" t="e">
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" t="e">
         <f>IF(
    IF(E20="&lt;",F20/2,F20) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D20,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D20,Criteria!A:A,Criteria!B:B))-1)),
@@ -3860,7 +3848,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I20" s="17" t="str">
+      <c r="I20" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D20,
@@ -3877,25 +3865,25 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="17" t="s">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="C21" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D21" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21">
         <v>23</v>
       </c>
-      <c r="G21" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="17" t="str">
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" t="str">
         <f>IF(
    IF(E21="&lt;",F21/2,F21) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D21,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D21,Criteria!A:A,Criteria!B:B))-1)),
@@ -3904,7 +3892,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I21" s="17" t="str">
+      <c r="I21" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D21,
@@ -3921,25 +3909,25 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="17" t="s">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D22" s="17" t="s">
+      <c r="C22" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D22" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22">
         <v>22</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="17" t="str">
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" t="str">
         <f>IF(
    IF(E22="&lt;",F22/2,F22) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D22,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D22,Criteria!A:A,Criteria!B:B))-1)),
@@ -3948,7 +3936,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I22" s="17" t="str">
+      <c r="I22" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D22,
@@ -3965,28 +3953,28 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="17" t="s">
+      <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D23" s="17" t="s">
+      <c r="C23" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D23" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23">
         <v>0.1</v>
       </c>
-      <c r="G23" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="17" t="str">
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" t="str">
         <f>IF(
    IF(E23="&lt;",F23/2,F23) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D23,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D23,Criteria!A:A,Criteria!B:B))-1)),
@@ -3995,7 +3983,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I23" s="17" t="str">
+      <c r="I23" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D23,
@@ -4012,25 +4000,25 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="17" t="s">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D24" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24">
         <v>37</v>
       </c>
-      <c r="G24" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="17" t="str">
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" t="str">
         <f>IF(
    IF(E24="&lt;",F24/2,F24) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D24,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D24,Criteria!A:A,Criteria!B:B))-1)),
@@ -4039,7 +4027,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I24" s="17" t="str">
+      <c r="I24" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D24,
@@ -4056,25 +4044,25 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="17" t="s">
+      <c r="A25" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D25" s="17" t="s">
+      <c r="C25" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D25" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25">
         <v>72</v>
       </c>
-      <c r="G25" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="17" t="str">
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="str">
         <f>IF(
    IF(E25="&lt;",F25/2,F25) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D25,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D25,Criteria!A:A,Criteria!B:B))-1)),
@@ -4083,7 +4071,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I25" s="17" t="str">
+      <c r="I25" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D25,
@@ -4100,25 +4088,25 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="17" t="s">
+      <c r="A26" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D26" s="17" t="s">
+      <c r="C26" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="G26" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="17" t="str">
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" t="str">
         <f>IF(
    IF(E26="&lt;",F26/2,F26) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D26,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D26,Criteria!A:A,Criteria!B:B))-1)),
@@ -4127,7 +4115,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I26" s="17" t="str">
+      <c r="I26" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D26,
@@ -4144,28 +4132,28 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="17" t="s">
+      <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D27" s="17" t="s">
+      <c r="C27" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D27" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="17" t="str">
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" t="str">
         <f>IF(
    IF(E27="&lt;",F27/2,F27) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D27,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D27,Criteria!A:A,Criteria!B:B))-1)),
@@ -4174,7 +4162,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I27" s="17" t="str">
+      <c r="I27" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D27,
@@ -4191,25 +4179,25 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="17" t="s">
+      <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D28" s="17" t="s">
+      <c r="C28" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D28" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28">
         <v>28</v>
       </c>
-      <c r="G28" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="17" t="e">
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" t="e">
         <f>IF(
    IF(E28="&lt;",F28/2,F28) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D28,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D28,Criteria!A:A,Criteria!B:B))-1)),
@@ -4218,7 +4206,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I28" s="17" t="str">
+      <c r="I28" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D28,
@@ -4235,25 +4223,25 @@
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="17" t="s">
+      <c r="A29" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D29" s="17" t="s">
+      <c r="C29" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D29" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29">
         <v>49</v>
       </c>
-      <c r="G29" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="17" t="str">
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" t="str">
         <f>IF(
    IF(E29="&lt;",F29/2,F29) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D29,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D29,Criteria!A:A,Criteria!B:B))-1)),
@@ -4262,7 +4250,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I29" s="17" t="str">
+      <c r="I29" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D29,
@@ -4279,25 +4267,25 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="17" t="s">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D30" s="17" t="s">
+      <c r="C30" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D30" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30">
         <v>184</v>
       </c>
-      <c r="G30" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="17" t="str">
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="str">
         <f>IF(
    IF(E30="&lt;",F30/2,F30) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D30,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D30,Criteria!A:A,Criteria!B:B))-1)),
@@ -4306,7 +4294,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I30" s="17" t="str">
+      <c r="I30" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D30,
@@ -4323,28 +4311,28 @@
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="17" t="s">
+      <c r="A31" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D31" s="17" t="s">
+      <c r="C31" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D31" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31">
         <v>0.1</v>
       </c>
-      <c r="G31" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="17" t="str">
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" t="str">
         <f>IF(
    IF(E31="&lt;",F31/2,F31) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D31,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D31,Criteria!A:A,Criteria!B:B))-1)),
@@ -4353,7 +4341,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I31" s="17" t="str">
+      <c r="I31" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D31,
@@ -4370,25 +4358,25 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="17" t="s">
+      <c r="A32" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D32" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32">
         <v>26</v>
       </c>
-      <c r="G32" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="17" t="str">
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" t="str">
         <f>IF(
    IF(E32="&lt;",F32/2,F32) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D32,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D32,Criteria!A:A,Criteria!B:B))-1)),
@@ -4397,7 +4385,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I32" s="17" t="str">
+      <c r="I32" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D32,
@@ -4414,25 +4402,25 @@
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="17" t="s">
+      <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D33" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33">
         <v>225</v>
       </c>
-      <c r="G33" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="17" t="str">
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" t="str">
         <f>IF(
    IF(E33="&lt;",F33/2,F33) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D33,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D33,Criteria!A:A,Criteria!B:B))-1)),
@@ -4441,7 +4429,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I33" s="17" t="str">
+      <c r="I33" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D33,
@@ -4458,25 +4446,25 @@
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="17" t="s">
+      <c r="A34" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D34" s="17" t="s">
+      <c r="C34" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D34" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34">
         <v>5</v>
       </c>
-      <c r="G34" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="17" t="str">
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="str">
         <f>IF(
    IF(E34="&lt;",F34/2,F34) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D34,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D34,Criteria!A:A,Criteria!B:B))-1)),
@@ -4485,7 +4473,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I34" s="17" t="str">
+      <c r="I34" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D34,
@@ -4502,28 +4490,28 @@
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="17" t="s">
+      <c r="A35" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D35" s="17" t="s">
+      <c r="C35" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D35" t="s">
         <v>2</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" t="s">
         <v>80</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="17" t="str">
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="str">
         <f>IF(
    IF(E35="&lt;",F35/2,F35) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D35,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D35,Criteria!A:A,Criteria!B:B))-1)),
@@ -4532,7 +4520,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I35" s="17" t="str">
+      <c r="I35" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D35,
@@ -4549,25 +4537,25 @@
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="17" t="s">
+      <c r="A36" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D36" s="17" t="s">
+      <c r="C36" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D36" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36">
         <v>56</v>
       </c>
-      <c r="G36" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="17" t="e">
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" t="e">
         <f>IF(
    IF(E36="&lt;",F36/2,F36) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D36,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D36,Criteria!A:A,Criteria!B:B))-1)),
@@ -4576,7 +4564,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I36" s="17" t="str">
+      <c r="I36" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D36,
@@ -4593,25 +4581,25 @@
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="17" t="s">
+      <c r="A37" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D37" s="17" t="s">
+      <c r="C37" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D37" t="s">
         <v>4</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37">
         <v>22</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="17" t="str">
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" t="str">
         <f>IF(
    IF(E37="&lt;",F37/2,F37) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D37,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D37,Criteria!A:A,Criteria!B:B))-1)),
@@ -4620,7 +4608,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I37" s="17" t="str">
+      <c r="I37" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D37,
@@ -4637,25 +4625,25 @@
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="17" t="s">
+      <c r="A38" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D38" s="17" t="s">
+      <c r="C38" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D38" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38">
         <v>26</v>
       </c>
-      <c r="G38" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="17" t="str">
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" t="str">
         <f>IF(
    IF(E38="&lt;",F38/2,F38) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D38,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D38,Criteria!A:A,Criteria!B:B))-1)),
@@ -4664,7 +4652,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I38" s="17" t="str">
+      <c r="I38" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D38,
@@ -4681,28 +4669,28 @@
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="17" t="s">
+      <c r="A39" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D39" s="17" t="s">
+      <c r="C39" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D39" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39">
         <v>0.1</v>
       </c>
-      <c r="G39" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="17" t="str">
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" t="str">
         <f>IF(
    IF(E39="&lt;",F39/2,F39) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D39,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D39,Criteria!A:A,Criteria!B:B))-1)),
@@ -4711,7 +4699,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I39" s="17" t="str">
+      <c r="I39" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D39,
@@ -4728,25 +4716,25 @@
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="17" t="s">
+      <c r="A40" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D40" s="17" t="s">
+      <c r="C40" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D40" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F40">
         <v>55</v>
       </c>
-      <c r="G40" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="17" t="str">
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="str">
         <f>IF(
    IF(E40="&lt;",F40/2,F40) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D40,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D40,Criteria!A:A,Criteria!B:B))-1)),
@@ -4755,7 +4743,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I40" s="17" t="str">
+      <c r="I40" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D40,
@@ -4772,25 +4760,25 @@
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="17" t="s">
+      <c r="A41" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D41" s="17" t="s">
+      <c r="C41" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D41" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="17">
+      <c r="F41">
         <v>344</v>
       </c>
-      <c r="G41" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H41" s="17" t="str">
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" t="str">
         <f>IF(
    IF(E41="&lt;",F41/2,F41) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D41,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D41,Criteria!A:A,Criteria!B:B))-1)),
@@ -4799,7 +4787,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I41" s="17" t="str">
+      <c r="I41" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D41,
@@ -4816,25 +4804,25 @@
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="17" t="s">
+      <c r="A42" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D42" s="17" t="s">
+      <c r="C42" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D42" t="s">
         <v>1</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42">
         <v>12</v>
       </c>
-      <c r="G42" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H42" s="17" t="str">
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="str">
         <f>IF(
    IF(E42="&lt;",F42/2,F42) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D42,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D42,Criteria!A:A,Criteria!B:B))-1)),
@@ -4843,7 +4831,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I42" s="17" t="str">
+      <c r="I42" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D42,
@@ -4860,25 +4848,25 @@
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="17" t="s">
+      <c r="A43" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D43" t="s">
         <v>2</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43">
         <v>2</v>
       </c>
-      <c r="G43" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H43" s="17" t="str">
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" t="str">
         <f>IF(
    IF(E43="&lt;",F43/2,F43) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D43,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D43,Criteria!A:A,Criteria!B:B))-1)),
@@ -4887,7 +4875,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I43" s="17" t="str">
+      <c r="I43" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D43,
@@ -4904,25 +4892,25 @@
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="17" t="s">
+      <c r="A44" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D44" s="17" t="s">
+      <c r="C44" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D44" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44">
         <v>34</v>
       </c>
-      <c r="G44" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="17" t="e">
+      <c r="G44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" t="e">
         <f>IF(
    IF(E44="&lt;",F44/2,F44) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D44,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D44,Criteria!A:A,Criteria!B:B))-1)),
@@ -4931,7 +4919,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I44" s="17" t="str">
+      <c r="I44" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D44,
@@ -4948,25 +4936,25 @@
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="17" t="s">
+      <c r="A45" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D45" s="17" t="s">
+      <c r="C45" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D45" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45">
         <v>1460</v>
       </c>
-      <c r="G45" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H45" s="17" t="str">
+      <c r="G45" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" t="str">
         <f>IF(
    IF(E45="&lt;",F45/2,F45) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D45,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D45,Criteria!A:A,Criteria!B:B))-1)),
@@ -4975,7 +4963,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I45" s="17" t="str">
+      <c r="I45" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D45,
@@ -4992,25 +4980,25 @@
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="17" t="s">
+      <c r="A46" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D46" s="17" t="s">
+      <c r="C46" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D46" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46">
         <v>557</v>
       </c>
-      <c r="G46" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H46" s="17" t="str">
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" t="str">
         <f>IF(
    IF(E46="&lt;",F46/2,F46) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D46,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D46,Criteria!A:A,Criteria!B:B))-1)),
@@ -5019,7 +5007,7 @@
 )</f>
         <v>Exceeds</v>
       </c>
-      <c r="I46" s="17" t="str">
+      <c r="I46" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D46,
@@ -5036,28 +5024,28 @@
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="17" t="s">
+      <c r="A47" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D47" s="17" t="s">
+      <c r="C47" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D47" t="s">
         <v>6</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" t="s">
         <v>80</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47">
         <v>0.1</v>
       </c>
-      <c r="G47" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H47" s="17" t="str">
+      <c r="G47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" t="str">
         <f>IF(
    IF(E47="&lt;",F47/2,F47) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D47,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D47,Criteria!A:A,Criteria!B:B))-1)),
@@ -5066,7 +5054,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I47" s="17" t="str">
+      <c r="I47" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D47,
@@ -5083,25 +5071,25 @@
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="17" t="s">
+      <c r="A48" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D48" s="17" t="s">
+      <c r="C48" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D48" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48">
         <v>80</v>
       </c>
-      <c r="G48" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H48" s="17" t="str">
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" t="str">
         <f>IF(
    IF(E48="&lt;",F48/2,F48) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D48,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D48,Criteria!A:A,Criteria!B:B))-1)),
@@ -5110,7 +5098,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I48" s="17" t="str">
+      <c r="I48" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D48,
@@ -5127,25 +5115,25 @@
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="17" t="s">
+      <c r="A49" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="16">
-        <v>45245.625</v>
-      </c>
-      <c r="D49" s="17" t="s">
+      <c r="C49" s="13">
+        <v>45245.625</v>
+      </c>
+      <c r="D49" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49">
         <v>30000</v>
       </c>
-      <c r="G49" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H49" s="17" t="str">
+      <c r="G49" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" t="str">
         <f>IF(
    IF(E49="&lt;",F49/2,F49) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D49,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D49,Criteria!A:A,Criteria!B:B))-1)),
@@ -5154,7 +5142,7 @@
 )</f>
         <v>Exceeds</v>
       </c>
-      <c r="I49" s="17" t="str">
+      <c r="I49" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D49,
@@ -5171,28 +5159,28 @@
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="17" t="s">
+      <c r="A50" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" t="s">
         <v>63</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" t="s">
         <v>1</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" t="s">
         <v>80</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50">
         <v>5</v>
       </c>
-      <c r="G50" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H50" s="17" t="str">
+      <c r="G50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" t="str">
         <f>IF(
    IF(E50="&lt;",F50/2,F50) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D50,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D50,Criteria!A:A,Criteria!B:B))-1)),
@@ -5201,7 +5189,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I50" s="17" t="str">
+      <c r="I50" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D50,
@@ -5218,28 +5206,28 @@
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="17" t="s">
+      <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" t="s">
         <v>63</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" t="s">
         <v>2</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" t="s">
         <v>80</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H51" s="17" t="str">
+      <c r="G51" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" t="str">
         <f>IF(
    IF(E51="&lt;",F51/2,F51) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D51,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D51,Criteria!A:A,Criteria!B:B))-1)),
@@ -5248,7 +5236,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I51" s="17" t="str">
+      <c r="I51" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D51,
@@ -5265,25 +5253,25 @@
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="17" t="s">
+      <c r="A52" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52">
         <v>52</v>
       </c>
-      <c r="G52" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H52" s="17" t="e">
+      <c r="G52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" t="e">
         <f>IF(
    IF(E52="&lt;",F52/2,F52) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D52,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D52,Criteria!A:A,Criteria!B:B))-1)),
@@ -5292,7 +5280,7 @@
 )</f>
         <v>#N/A</v>
       </c>
-      <c r="I52" s="17" t="str">
+      <c r="I52" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D52,
@@ -5309,25 +5297,25 @@
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="17" t="s">
+      <c r="A53" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" t="s">
         <v>4</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53">
         <v>43</v>
       </c>
-      <c r="G53" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="17" t="str">
+      <c r="G53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" t="str">
         <f>IF(
    IF(E53="&lt;",F53/2,F53) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D53,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D53,Criteria!A:A,Criteria!B:B))-1)),
@@ -5336,7 +5324,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I53" s="17" t="str">
+      <c r="I53" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D53,
@@ -5353,25 +5341,25 @@
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="17" t="s">
+      <c r="A54" t="s">
         <v>51</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54">
         <v>68</v>
       </c>
-      <c r="G54" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H54" s="17" t="str">
+      <c r="G54" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" t="str">
         <f>IF(
    IF(E54="&lt;",F54/2,F54) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D54,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D54,Criteria!A:A,Criteria!B:B))-1)),
@@ -5380,7 +5368,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I54" s="17" t="str">
+      <c r="I54" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D54,
@@ -5397,28 +5385,28 @@
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="17" t="s">
+      <c r="A55" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" t="s">
         <v>6</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55">
         <v>0.1</v>
       </c>
-      <c r="G55" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H55" s="17" t="str">
+      <c r="G55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" t="str">
         <f>IF(
    IF(E55="&lt;",F55/2,F55) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D55,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D55,Criteria!A:A,Criteria!B:B))-1)),
@@ -5427,7 +5415,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I55" s="17" t="str">
+      <c r="I55" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D55,
@@ -5444,25 +5432,25 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="17" t="s">
+      <c r="A56" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56">
         <v>79</v>
       </c>
-      <c r="G56" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H56" s="17" t="str">
+      <c r="G56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" t="str">
         <f>IF(
    IF(E56="&lt;",F56/2,F56) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D56,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D56,Criteria!A:A,Criteria!B:B))-1)),
@@ -5471,7 +5459,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I56" s="17" t="str">
+      <c r="I56" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D56,
@@ -5488,25 +5476,25 @@
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="17" t="s">
+      <c r="A57" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" t="s">
         <v>63</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="13">
         <v>45245.779166666704</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57">
         <v>1950</v>
       </c>
-      <c r="G57" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H57" s="17" t="str">
+      <c r="G57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" t="str">
         <f>IF(
    IF(E57="&lt;",F57/2,F57) &gt;
    VALUE(LEFT(_xlfn.XLOOKUP(D57,Criteria!A:A,Criteria!B:B),FIND(" ",_xlfn.XLOOKUP(D57,Criteria!A:A,Criteria!B:B))-1)),
@@ -5515,7 +5503,7 @@
 )</f>
         <v>OK</v>
       </c>
-      <c r="I57" s="17" t="str">
+      <c r="I57" t="str">
         <f>IFERROR(
   _xlfn.LET(
     _xlpm.chem, D57,
@@ -5553,74 +5541,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="22" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="23" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="23" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="23" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5655,87 +5643,87 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="24" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10">
         <v>7</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10">
         <v>7</v>
       </c>
     </row>
@@ -5750,407 +5738,407 @@
   <dimension ref="A3:K16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="3" width="22.140625" style="4" customWidth="1"/>
-    <col min="4" max="11" width="10.7109375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="3" width="22.140625" style="1" customWidth="1"/>
+    <col min="4" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:11">
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="1"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:11" customFormat="1" ht="108.95" customHeight="1">
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18">
         <v>100</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="18">
         <v>20</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="18">
         <v>100</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="19">
         <v>6000</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="18">
         <v>300</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="18">
         <v>40</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="18">
         <v>400</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="19">
         <v>7400</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="15">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="10">
         <v>45245</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="10">
         <v>45245</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="10">
         <v>45245</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="10">
         <v>45245</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="10">
         <v>45245</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="10">
         <v>45245</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="K15" s="20" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="10">
         <v>45245</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="11" t="s">
         <v>69</v>
       </c>
     </row>
